--- a/4.evidence/PLC-S/SalesShipMatch_SampleTransactionList_FY2025.xlsx
+++ b/4.evidence/PLC-S/SalesShipMatch_SampleTransactionList_FY2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -143,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,11 +160,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,7 +729,7 @@
           <t>SH-202504-0147</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <v>45755</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -763,7 +765,7 @@
           <t>JV-202504-0163</t>
         </is>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="11" t="n">
         <v>45755</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -779,7 +781,7 @@
           <t>SH-202504-0028</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>45770</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -815,7 +817,7 @@
           <t>JV-202504-0234</t>
         </is>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="11" t="n">
         <v>45770</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -831,7 +833,7 @@
           <t>SH-202505-0178</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>45789</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -867,7 +869,7 @@
           <t>JV-202505-0245</t>
         </is>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="11" t="n">
         <v>45789</v>
       </c>
       <c r="L13" s="10" t="n">
@@ -883,7 +885,7 @@
           <t>SH-202505-0172</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>45804</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -919,7 +921,7 @@
           <t>JV-202505-0197</t>
         </is>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="11" t="n">
         <v>45804</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -935,7 +937,7 @@
           <t>SH-202506-0180</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>45818</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -971,7 +973,7 @@
           <t>JV-202506-0113</t>
         </is>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="11" t="n">
         <v>45818</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -987,7 +989,7 @@
           <t>SH-202506-0125</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="11" t="n">
         <v>45833</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1023,7 +1025,7 @@
           <t>JV-202506-0255</t>
         </is>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="11" t="n">
         <v>45833</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -1039,7 +1041,7 @@
           <t>SH-202507-0240</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="11" t="n">
         <v>45847</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1075,7 +1077,7 @@
           <t>JV-202507-0214</t>
         </is>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="11" t="n">
         <v>45847</v>
       </c>
       <c r="L17" s="10" t="n">
@@ -1091,7 +1093,7 @@
           <t>SH-202507-0032</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="11" t="n">
         <v>45862</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1127,7 +1129,7 @@
           <t>JV-202507-0162</t>
         </is>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="11" t="n">
         <v>45862</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -1143,7 +1145,7 @@
           <t>SH-202508-0197</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="11" t="n">
         <v>45880</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1179,7 +1181,7 @@
           <t>JV-202508-0216</t>
         </is>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="11" t="n">
         <v>45880</v>
       </c>
       <c r="L19" s="10" t="n">
@@ -1195,7 +1197,7 @@
           <t>SH-202508-0175</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="11" t="n">
         <v>45895</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1231,7 +1233,7 @@
           <t>JV-202508-0114</t>
         </is>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="11" t="n">
         <v>45895</v>
       </c>
       <c r="L20" s="10" t="n">
@@ -1247,7 +1249,7 @@
           <t>SH-202509-0089</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="11" t="n">
         <v>45913</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1283,7 +1285,7 @@
           <t>JV-202509-0280</t>
         </is>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="11" t="n">
         <v>45913</v>
       </c>
       <c r="L21" s="10" t="n">
@@ -1299,7 +1301,7 @@
           <t>SH-202509-0185</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="11" t="n">
         <v>45928</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1335,7 +1337,7 @@
           <t>JV-202509-0115</t>
         </is>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="11" t="n">
         <v>45928</v>
       </c>
       <c r="L22" s="10" t="n">
@@ -1351,7 +1353,7 @@
           <t>SH-202510-0191</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="11" t="n">
         <v>45944</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1387,7 +1389,7 @@
           <t>JV-202510-0271</t>
         </is>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="11" t="n">
         <v>45944</v>
       </c>
       <c r="L23" s="10" t="n">
@@ -1403,7 +1405,7 @@
           <t>SH-202510-0068</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="11" t="n">
         <v>45959</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1439,7 +1441,7 @@
           <t>JV-202510-0145</t>
         </is>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="K24" s="11" t="n">
         <v>45960</v>
       </c>
       <c r="L24" s="10" t="n">
@@ -1455,7 +1457,7 @@
           <t>SH-202511-0078</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="11" t="n">
         <v>45967</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1491,7 +1493,7 @@
           <t>JV-202511-0146</t>
         </is>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="11" t="n">
         <v>45967</v>
       </c>
       <c r="L25" s="10" t="n">
@@ -1507,7 +1509,7 @@
           <t>SH-202511-0234</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="11" t="n">
         <v>45978</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1543,7 +1545,7 @@
           <t>JV-202511-0234</t>
         </is>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="11" t="n">
         <v>45978</v>
       </c>
       <c r="L26" s="10" t="n">
@@ -1559,7 +1561,7 @@
           <t>SH-202511-0021</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="11" t="n">
         <v>45989</v>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1595,7 +1597,7 @@
           <t>JV-202511-0223</t>
         </is>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="11" t="n">
         <v>45989</v>
       </c>
       <c r="L27" s="10" t="n">
@@ -1611,7 +1613,7 @@
           <t>SH-202512-0065</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="11" t="n">
         <v>46003</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1647,7 +1649,7 @@
           <t>JV-202512-0171</t>
         </is>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="11" t="n">
         <v>46003</v>
       </c>
       <c r="L28" s="10" t="n">
@@ -1663,7 +1665,7 @@
           <t>SH-202512-0059</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="11" t="n">
         <v>46015</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1699,7 +1701,7 @@
           <t>JV-202512-0262</t>
         </is>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="11" t="n">
         <v>46015</v>
       </c>
       <c r="L29" s="10" t="n">
@@ -1715,7 +1717,7 @@
           <t>SH-202601-0110</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="11" t="n">
         <v>46036</v>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1751,7 +1753,7 @@
           <t>JV-202601-0249</t>
         </is>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="11" t="n">
         <v>46036</v>
       </c>
       <c r="L30" s="10" t="n">
@@ -1764,10 +1766,10 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>SH-202601-0110</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
+          <t>SH-202601-0275</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
         <v>46051</v>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1803,7 +1805,7 @@
           <t>JV-202601-0236</t>
         </is>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="11" t="n">
         <v>46051</v>
       </c>
       <c r="L31" s="10" t="n">
@@ -1819,7 +1821,7 @@
           <t>SH-202602-0215</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="11" t="n">
         <v>46063</v>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1855,7 +1857,7 @@
           <t>JV-202602-0120</t>
         </is>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="11" t="n">
         <v>46063</v>
       </c>
       <c r="L32" s="10" t="n">
@@ -1871,7 +1873,7 @@
           <t>SH-202602-0152</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="11" t="n">
         <v>46078</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1907,7 +1909,7 @@
           <t>JV-202602-0290</t>
         </is>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="11" t="n">
         <v>46078</v>
       </c>
       <c r="L33" s="10" t="n">
@@ -1923,7 +1925,7 @@
           <t>SH-202603-0069</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="11" t="n">
         <v>46091</v>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1959,7 +1961,7 @@
           <t>JV-202603-0262</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="11" t="n">
         <v>46091</v>
       </c>
       <c r="L34" s="10" t="n">
@@ -1975,7 +1977,7 @@
           <t>SH-202603-0049</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="11" t="n">
         <v>46105</v>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2011,7 +2013,7 @@
           <t>JV-202603-0280</t>
         </is>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="11" t="n">
         <v>46105</v>
       </c>
       <c r="L35" s="10" t="n">
@@ -2022,8 +2024,8 @@
   <mergeCells count="10">
     <mergeCell ref="D7:L7"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="D5:L5"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:L5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="D4:L4"/>
     <mergeCell ref="A6:C6"/>
